--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484232_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484232_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0649</v>
+        <v>6.3248</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2822</v>
+        <v>3.6238</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7827</v>
+        <v>2.701</v>
       </c>
       <c r="G2" t="n">
         <v>3.6168</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5263</v>
+        <v>0.7862</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8671</v>
+        <v>1.2087</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3408</v>
+        <v>-0.4225</v>
       </c>
       <c r="V2" t="n">
         <v>0.5545</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0191</v>
+        <v>6.0289</v>
       </c>
       <c r="E3" t="n">
-        <v>3.822</v>
+        <v>4.1859</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1971</v>
+        <v>1.843</v>
       </c>
       <c r="G3" t="n">
         <v>2.2787</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9552</v>
+        <v>0.965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6219</v>
+        <v>0.9858</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3333</v>
+        <v>-0.0208</v>
       </c>
       <c r="V3" t="n">
         <v>0.8317</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4069</v>
+        <v>3.6931</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7244</v>
+        <v>0.6838</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6825</v>
+        <v>3.0093</v>
       </c>
       <c r="G4" t="n">
         <v>2.4081</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6169</v>
+        <v>0.9031</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3565</v>
+        <v>1.316</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7396</v>
+        <v>-0.4128</v>
       </c>
       <c r="V4" t="n">
         <v>1.1632</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1757</v>
+        <v>3.178</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3247</v>
+        <v>1.0819</v>
       </c>
       <c r="F5" t="n">
-        <v>1.851</v>
+        <v>2.0962</v>
       </c>
       <c r="G5" t="n">
         <v>1.7574</v>
@@ -844,13 +844,13 @@
         <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2928</v>
+        <v>0.2951</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0402</v>
+        <v>0.7973</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7474</v>
+        <v>-0.5022</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2186</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. FONT TÀPIA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.729</v>
+        <v>2.3755</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2749</v>
+        <v>-0.3436</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4541</v>
+        <v>2.719</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6794</v>
+        <v>0.775</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4249</v>
+        <v>1.4626</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2544</v>
+        <v>-0.6875</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2749</v>
+        <v>-0.224</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>1.0028</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2544</v>
+        <v>-1.2268</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4045</v>
+        <v>0.999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4045</v>
+        <v>0.4597</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.5393</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1315</v>
+        <v>0.0963</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1196</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1315</v>
+        <v>0.2159</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>L. FONT TÀPIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5363</v>
+        <v>1.6745</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4938</v>
+        <v>1.2749</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0301</v>
+        <v>0.3996</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9866</v>
+        <v>1.6794</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4088</v>
+        <v>0.4249</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5778</v>
+        <v>1.2544</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0022</v>
+        <v>1.2749</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2333</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7688</v>
+        <v>1.2544</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.4045</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1755</v>
+        <v>0.4045</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8089</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5232</v>
+        <v>0.077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2337</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7569</v>
+        <v>0.077</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6062</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2741</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>B. RODRÍGUEZ CHAVARRIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4692</v>
+        <v>1.3296</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9503</v>
+        <v>1.1669</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4195</v>
+        <v>0.1627</v>
       </c>
       <c r="G8" t="n">
-        <v>0.775</v>
+        <v>2.9327</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4626</v>
+        <v>1.867</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6875</v>
+        <v>1.0657</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.224</v>
+        <v>1.6641</v>
       </c>
       <c r="K8" t="n">
         <v>1.0028</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2268</v>
+        <v>0.6613</v>
       </c>
       <c r="M8" t="n">
-        <v>0.999</v>
+        <v>1.2687</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4597</v>
+        <v>0.8642</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5393</v>
+        <v>0.4045</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.4795</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0837</v>
+        <v>-0.4733</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ CHAVARRIA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3702</v>
+        <v>1.2833</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2075</v>
+        <v>-0.3927</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1627</v>
+        <v>1.676</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9327</v>
+        <v>3.9866</v>
       </c>
       <c r="H9" t="n">
-        <v>1.867</v>
+        <v>2.4088</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0657</v>
+        <v>1.5778</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6641</v>
+        <v>3.0022</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0028</v>
+        <v>2.2333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6613</v>
+        <v>0.7688</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2687</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8642</v>
+        <v>0.1755</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4045</v>
+        <v>0.8089</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0467</v>
+        <v>0.2703</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5201</v>
+        <v>-0.1326</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4733</v>
+        <v>0.4029</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-1.6062</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.2741</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3368</v>
+        <v>1.1774</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5718</v>
+        <v>0.1674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7649</v>
+        <v>1.0101</v>
       </c>
       <c r="G10" t="n">
         <v>0.089</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7991</v>
+        <v>0.6398</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7705</v>
+        <v>0.3661</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0286</v>
+        <v>0.2737</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3327</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3226</v>
+        <v>0.5362</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.231</v>
+        <v>0.5616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9084</v>
+        <v>-0.0255</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6727</v>
+        <v>0.3351</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2456</v>
+        <v>-1.7565</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4272</v>
+        <v>2.0916</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9187</v>
+        <v>1.3879</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1036</v>
+        <v>-0.5692</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0223</v>
+        <v>1.9572</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.754</v>
+        <v>-1.0528</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3492</v>
+        <v>-1.1872</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4049</v>
+        <v>0.1344</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0968</v>
+        <v>0.542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5309</v>
+        <v>0.3661</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6278</v>
+        <v>0.1759</v>
       </c>
       <c r="V11" t="n">
-        <v>0.886</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3327</v>
+        <v>-1.8834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3272</v>
+        <v>-0.2371</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2473</v>
+        <v>-0.9277</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0799</v>
+        <v>0.6906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3351</v>
+        <v>-2.6727</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7565</v>
+        <v>-0.2456</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0916</v>
+        <v>-2.4272</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3879</v>
+        <v>-1.9187</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5692</v>
+        <v>0.1036</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9572</v>
+        <v>-2.0223</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0528</v>
+        <v>-0.754</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1872</v>
+        <v>-0.3492</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1344</v>
+        <v>-0.4049</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3214</v>
+        <v>0.1823</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4429</v>
+        <v>-0.2276</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1215</v>
+        <v>0.4099</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.886</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8834</v>
+        <v>-0.3327</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5737</v>
+        <v>-1.1771</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9199</v>
+        <v>-3.4143</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3461</v>
+        <v>2.2372</v>
       </c>
       <c r="G13" t="n">
         <v>0.326</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5789</v>
+        <v>-0.1823</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.4023</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3289</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.2186</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.8846</v>
+        <v>26.1871</v>
       </c>
       <c r="E14" t="n">
-        <v>7.365199999999998</v>
+        <v>7.6679</v>
       </c>
       <c r="F14" t="n">
         <v>18.5192</v>
@@ -1513,7 +1513,7 @@
         <v>17.5121</v>
       </c>
       <c r="H14" t="n">
-        <v>2.672</v>
+        <v>2.672000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>14.84</v>
@@ -1531,7 +1531,7 @@
         <v>6.520600000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>3.152100000000001</v>
+        <v>3.1521</v>
       </c>
       <c r="O14" t="n">
         <v>3.3685</v>
@@ -1546,22 +1546,22 @@
         <v>19.5342</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2782</v>
+        <v>4.581</v>
       </c>
       <c r="T14" t="n">
-        <v>4.334700000000001</v>
+        <v>4.6374</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05630000000000002</v>
+        <v>-0.05630000000000016</v>
       </c>
       <c r="V14" t="n">
         <v>1.1639</v>
       </c>
       <c r="W14" t="n">
-        <v>8.642999999999999</v>
+        <v>8.643000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.479199999999999</v>
+        <v>-7.4792</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8132</v>
+        <v>1.5823</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6243</v>
+        <v>2.0176</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8112</v>
+        <v>-0.4353</v>
       </c>
       <c r="G15" t="n">
         <v>0.4164</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7659</v>
+        <v>0.5351</v>
       </c>
       <c r="T15" t="n">
-        <v>0.71</v>
+        <v>0.1033</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0559</v>
+        <v>0.4318</v>
       </c>
       <c r="V15" t="n">
         <v>2.1935</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0705</v>
+        <v>0.9508</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5198</v>
+        <v>0.4602</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5904</v>
+        <v>0.4906</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1455</v>
+        <v>-0.4927</v>
       </c>
       <c r="H16" t="n">
-        <v>1.955</v>
+        <v>-0.1686</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8095</v>
+        <v>-0.3241</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6398</v>
+        <v>0.471</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3139</v>
+        <v>0.3901</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4943</v>
+        <v>-0.9638</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3589</v>
+        <v>-0.5587</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0702</v>
+        <v>0.1245</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0108</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0811</v>
+        <v>0.2173</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3405</v>
+        <v>-0.2437</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3405</v>
+        <v>-0.521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6502</v>
+        <v>0.4247</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1568</v>
+        <v>-0.6209</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4933</v>
+        <v>1.0457</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4927</v>
+        <v>1.1455</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1686</v>
+        <v>1.955</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3241</v>
+        <v>-0.8095</v>
       </c>
       <c r="J17" t="n">
-        <v>0.471</v>
+        <v>1.6398</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3901</v>
+        <v>2.3139</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9638</v>
+        <v>-0.4943</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5587</v>
+        <v>-0.3589</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4051</v>
+        <v>-0.1354</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1761</v>
+        <v>0.4244</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3961</v>
+        <v>-0.112</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.5364</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2437</v>
+        <v>-1.3405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.521</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.498</v>
+        <v>0.0214</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8481</v>
+        <v>-0.3089</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3501</v>
+        <v>0.3303</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7451</v>
+        <v>1.2604</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.34</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4051</v>
+        <v>0.7548</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3255</v>
+        <v>1.1451</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3255</v>
+        <v>1.0642</v>
       </c>
       <c r="L18" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.6739000000000001</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3357</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.0537</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.1219</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>-0.4196</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.0146</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.4051</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.5395</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3523</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.8448</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.4925</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.3321</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.6093</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5063</v>
+        <v>-0.3441</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5111</v>
+        <v>-0.039</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0048</v>
+        <v>-0.3051</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2604</v>
+        <v>-3.8974</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5054999999999999</v>
+        <v>-0.2553</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7548</v>
+        <v>-3.6421</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1451</v>
+        <v>-1.8586</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0642</v>
+        <v>-1.1845</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1152</v>
+        <v>-2.0388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5587</v>
+        <v>0.9292</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6739000000000001</v>
+        <v>-2.968</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.176</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4842</v>
+        <v>0.1171</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3792</v>
+        <v>-0.2931</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1219</v>
+        <v>3.534</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X19" t="n">
         <v>-0.1219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8441</v>
+        <v>-0.8323</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-2.4547</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1984</v>
+        <v>1.6224</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8974</v>
+        <v>-2.7451</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2553</v>
+        <v>-2.34</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.6421</v>
+        <v>-0.4051</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8586</v>
+        <v>-2.3255</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1845</v>
+        <v>-2.3255</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0388</v>
+        <v>-0.4196</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9292</v>
+        <v>-0.0146</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.968</v>
+        <v>-0.4051</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6761</v>
+        <v>0.0179</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4896</v>
+        <v>0.2381</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1865</v>
+        <v>-0.2202</v>
       </c>
       <c r="V20" t="n">
-        <v>3.534</v>
+        <v>0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6559</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1219</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1912</v>
+        <v>-1.9941</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4579</v>
+        <v>-0.9634</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7334</v>
+        <v>-1.0307</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4253</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5706</v>
+        <v>-0.3735</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5752</v>
+        <v>0.0696</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1458</v>
+        <v>-0.4431</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4466</v>
+        <v>-3.4545</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3481</v>
+        <v>-1.247</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0985</v>
+        <v>-2.2074</v>
       </c>
       <c r="G22" t="n">
         <v>-0.335</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3423</v>
+        <v>-0.3501</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0083</v>
+        <v>0.1095</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3506</v>
+        <v>-0.4596</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7693</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4356</v>
+        <v>-4.0427</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3686</v>
+        <v>-6.1664</v>
       </c>
       <c r="F23" t="n">
-        <v>1.933</v>
+        <v>2.1237</v>
       </c>
       <c r="G23" t="n">
         <v>-3.731</v>
@@ -2248,13 +2248,13 @@
         <v>2.3441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4506</v>
+        <v>-0.0577</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1319</v>
+        <v>0.0703</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3187</v>
+        <v>-0.128</v>
       </c>
       <c r="V23" t="n">
         <v>0.3321</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7086</v>
+        <v>-5.8789</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1782</v>
+        <v>-3.0771</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5304</v>
+        <v>-2.8019</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9742</v>
@@ -2326,13 +2326,13 @@
         <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1633</v>
+        <v>-0.3336</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1854</v>
+        <v>-0.4568</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6177</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.7879</v>
+        <v>-8.9466</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4228</v>
+        <v>-6.1195</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3651</v>
+        <v>-2.8271</v>
       </c>
       <c r="G25" t="n">
         <v>-5.7337</v>
@@ -2404,13 +2404,13 @@
         <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2244</v>
+        <v>-0.3832</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5915</v>
+        <v>-0.2881</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.633</v>
+        <v>-0.0951</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4624</v>
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.8844</v>
+        <v>-22.514</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.5192</v>
+        <v>-18.5191</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.3654</v>
+        <v>-3.9948</v>
       </c>
       <c r="G26" t="n">
         <v>-17.5121</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6721</v>
+        <v>-2.672099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-14.8401</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.5208</v>
+        <v>-6.520799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.1521</v>
+        <v>-3.152099999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.368600000000001</v>
+        <v>-3.3686</v>
       </c>
       <c r="M26" t="n">
         <v>-10.9917</v>
@@ -2482,13 +2482,13 @@
         <v>16.6042</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.2784</v>
+        <v>-0.9079</v>
       </c>
       <c r="T26" t="n">
-        <v>0.05629999999999991</v>
+        <v>0.05620000000000003</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.3347</v>
+        <v>-0.9641</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1638</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484232_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484232_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-0.0554</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.178</v>
+        <v>2.3755</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0819</v>
+        <v>-0.3436</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0962</v>
+        <v>2.719</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7574</v>
+        <v>0.775</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.833</v>
+        <v>1.4626</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5904</v>
+        <v>-0.6875</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2845</v>
+        <v>-0.224</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.3063</v>
+        <v>1.0028</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5908</v>
+        <v>-1.2268</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4729</v>
+        <v>0.999</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4733</v>
+        <v>0.4597</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0004</v>
+        <v>0.5393</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2951</v>
+        <v>0.0963</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7973</v>
+        <v>-0.1196</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5022</v>
+        <v>0.2159</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>L. FONT TAPIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3755</v>
+        <v>1.6745</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3436</v>
+        <v>1.2749</v>
       </c>
       <c r="F6" t="n">
-        <v>2.719</v>
+        <v>0.3996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.775</v>
+        <v>1.6794</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4626</v>
+        <v>0.4249</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6875</v>
+        <v>1.2544</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.224</v>
+        <v>1.2749</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0028</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2268</v>
+        <v>1.2544</v>
       </c>
       <c r="M6" t="n">
-        <v>0.999</v>
+        <v>0.4045</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4597</v>
+        <v>0.4045</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0963</v>
+        <v>0.077</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1196</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2159</v>
+        <v>0.077</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FONT TÀPIA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6745</v>
+        <v>1.6501</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2749</v>
+        <v>-0.4461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3996</v>
+        <v>2.0962</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6794</v>
+        <v>0.2295</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4249</v>
+        <v>-1.7539</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2544</v>
+        <v>1.9834</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2749</v>
+        <v>-1.2434</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-3.2272</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2544</v>
+        <v>1.9838</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4045</v>
+        <v>1.4729</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4045</v>
+        <v>1.4733</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>0.077</v>
+        <v>0.2951</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.7973</v>
       </c>
       <c r="U7" t="n">
-        <v>0.077</v>
+        <v>-0.5022</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ CHAVARRIA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3296</v>
+        <v>1.5279</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1669</v>
+        <v>1.5279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1627</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9327</v>
+        <v>1.5279</v>
       </c>
       <c r="H8" t="n">
-        <v>1.867</v>
+        <v>0.921</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0657</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6641</v>
+        <v>1.5279</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0028</v>
+        <v>0.921</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6613</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2687</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8642</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4795</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4733</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>B. RODRIGUEZ CHAVARRIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2833</v>
+        <v>1.3296</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3927</v>
+        <v>1.1669</v>
       </c>
       <c r="F9" t="n">
-        <v>1.676</v>
+        <v>0.1627</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9866</v>
+        <v>2.9327</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4088</v>
+        <v>1.867</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5778</v>
+        <v>1.0657</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0022</v>
+        <v>1.6641</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2333</v>
+        <v>1.0028</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7688</v>
+        <v>0.6613</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9844000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1755</v>
+        <v>0.8642</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8089</v>
+        <v>0.4045</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2703</v>
+        <v>0.0062</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1326</v>
+        <v>0.4795</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4029</v>
+        <v>-0.4733</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6062</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2741</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1774</v>
+        <v>1.2833</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1674</v>
+        <v>-0.3927</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0101</v>
+        <v>1.676</v>
       </c>
       <c r="G10" t="n">
-        <v>0.089</v>
+        <v>3.9866</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2781</v>
+        <v>2.4088</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1891</v>
+        <v>1.5778</v>
       </c>
       <c r="J10" t="n">
-        <v>0.778</v>
+        <v>3.0022</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6971000000000001</v>
+        <v>2.2333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0.7688</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6891</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.419</v>
+        <v>0.1755</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.27</v>
+        <v>0.8089</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6398</v>
+        <v>0.2703</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3661</v>
+        <v>-0.1326</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2737</v>
+        <v>0.4029</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3327</v>
+        <v>-1.6062</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3327</v>
+        <v>-1.2741</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5362</v>
+        <v>1.1774</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5616</v>
+        <v>0.1674</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0255</v>
+        <v>1.0101</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3351</v>
+        <v>0.089</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7565</v>
+        <v>0.2781</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0916</v>
+        <v>-0.1891</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3879</v>
+        <v>0.778</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5692</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9572</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0528</v>
+        <v>-0.6891</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1872</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1344</v>
+        <v>-0.27</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.542</v>
+        <v>0.6398</v>
       </c>
       <c r="T11" t="n">
         <v>0.3661</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1759</v>
+        <v>0.2737</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8310999999999999</v>
+        <v>-0.3327</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8834</v>
+        <v>-0.3327</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2371</v>
+        <v>0.5362</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9277</v>
+        <v>0.5616</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6906</v>
+        <v>-0.0255</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6727</v>
+        <v>0.3351</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2456</v>
+        <v>-1.7565</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4272</v>
+        <v>2.0916</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9187</v>
+        <v>1.3879</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1036</v>
+        <v>-0.5692</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0223</v>
+        <v>1.9572</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.754</v>
+        <v>-1.0528</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3492</v>
+        <v>-1.1872</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4049</v>
+        <v>0.1344</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1823</v>
+        <v>0.542</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2276</v>
+        <v>0.3661</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4099</v>
+        <v>0.1759</v>
       </c>
       <c r="V12" t="n">
-        <v>0.886</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3327</v>
+        <v>-1.8834</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1771</v>
+        <v>-0.2371</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4143</v>
+        <v>-0.9277</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2372</v>
+        <v>0.6906</v>
       </c>
       <c r="G13" t="n">
-        <v>0.326</v>
+        <v>-2.6727</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9018</v>
+        <v>-0.2456</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2278</v>
+        <v>-2.4272</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3238</v>
+        <v>-1.9187</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8774999999999999</v>
+        <v>0.1036</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5537</v>
+        <v>-2.0223</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6498</v>
+        <v>-0.754</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0243</v>
+        <v>-0.3492</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6741</v>
+        <v>-0.4049</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1823</v>
+        <v>0.1823</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4023</v>
+        <v>-0.2276</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.4099</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2186</v>
+        <v>0.886</v>
       </c>
       <c r="W13" t="n">
         <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3327</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.1871</v>
+        <v>-1.1771</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6679</v>
+        <v>-3.4143</v>
       </c>
       <c r="F14" t="n">
-        <v>18.5192</v>
+        <v>2.2372</v>
       </c>
       <c r="G14" t="n">
-        <v>17.5121</v>
+        <v>0.326</v>
       </c>
       <c r="H14" t="n">
-        <v>2.672000000000001</v>
+        <v>-0.9018</v>
       </c>
       <c r="I14" t="n">
-        <v>14.84</v>
+        <v>1.2278</v>
       </c>
       <c r="J14" t="n">
-        <v>10.9917</v>
+        <v>-0.3238</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4798999999999998</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>11.4715</v>
+        <v>0.5537</v>
       </c>
       <c r="M14" t="n">
-        <v>6.520600000000003</v>
+        <v>0.6498</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1521</v>
+        <v>-0.0243</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3685</v>
+        <v>0.6741</v>
       </c>
       <c r="P14" t="n">
-        <v>2.93</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.6041</v>
+        <v>-3.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>19.5342</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>4.581</v>
+        <v>-0.1823</v>
       </c>
       <c r="T14" t="n">
-        <v>4.6374</v>
+        <v>-0.4023</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05630000000000016</v>
+        <v>0.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1639</v>
+        <v>1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>8.643000000000001</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.4792</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5823</v>
+        <v>26.1871</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0176</v>
+        <v>7.667800000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4353</v>
+        <v>18.5192</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4164</v>
+        <v>17.5121</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2707</v>
+        <v>2.6721</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6871</v>
+        <v>14.84</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3253</v>
+        <v>10.9917</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7905</v>
+        <v>-0.4798</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1159</v>
+        <v>11.4715</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9089</v>
+        <v>6.520600000000003</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5199</v>
+        <v>3.1521</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4287</v>
+        <v>3.3685</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>2.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1255</v>
+        <v>-16.6041</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>19.5342</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5351</v>
+        <v>4.581</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1033</v>
+        <v>4.6374</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4318</v>
+        <v>-0.05629999999999993</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1935</v>
+        <v>1.1639</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7145</v>
+        <v>8.643000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.521</v>
-      </c>
+        <v>-7.4792</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9508</v>
+        <v>1.5823</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4602</v>
+        <v>2.0176</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4906</v>
+        <v>-0.4353</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4927</v>
+        <v>0.4164</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1686</v>
+        <v>-0.2707</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3241</v>
+        <v>0.6871</v>
       </c>
       <c r="J16" t="n">
-        <v>0.471</v>
+        <v>2.3253</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3901</v>
+        <v>-0.7905</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>3.1159</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9638</v>
+        <v>-1.9089</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5587</v>
+        <v>0.5199</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>-2.4287</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.5627</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.7581</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.1245</v>
+        <v>0.5351</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1033</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2173</v>
+        <v>0.4318</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2437</v>
+        <v>2.1935</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>2.7145</v>
       </c>
       <c r="X16" t="n">
         <v>-0.521</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4247</v>
+        <v>0.9508</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6209</v>
+        <v>0.4602</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0457</v>
+        <v>0.4906</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1455</v>
+        <v>-0.4927</v>
       </c>
       <c r="H17" t="n">
-        <v>1.955</v>
+        <v>-0.1686</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8095</v>
+        <v>-0.3241</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6398</v>
+        <v>0.471</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3139</v>
+        <v>0.3901</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4943</v>
+        <v>-0.9638</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3589</v>
+        <v>-0.5587</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1354</v>
+        <v>-0.4051</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4244</v>
+        <v>0.1245</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.112</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5364</v>
+        <v>0.2173</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3405</v>
+        <v>-0.2437</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3405</v>
+        <v>-0.521</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0214</v>
+        <v>0.4247</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3089</v>
+        <v>-0.6209</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3303</v>
+        <v>1.0457</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2604</v>
+        <v>1.1455</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5054999999999999</v>
+        <v>1.955</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7548</v>
+        <v>-0.8095</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1451</v>
+        <v>1.6398</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0642</v>
+        <v>2.3139</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1152</v>
+        <v>-0.4943</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5587</v>
+        <v>-0.3589</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.1354</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3357</v>
+        <v>0.4244</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.282</v>
+        <v>-0.112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0537</v>
+        <v>0.5364</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3441</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.039</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3051</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8974</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2553</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6421</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8586</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1845</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0388</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9292</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.968</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.176</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1171</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2931</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.534</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8323</v>
+        <v>0.0214</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4547</v>
+        <v>-0.3089</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6224</v>
+        <v>0.3303</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7451</v>
+        <v>1.2604</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.34</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4051</v>
+        <v>0.7548</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3255</v>
+        <v>1.1451</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3255</v>
+        <v>1.0642</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4196</v>
+        <v>0.1152</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0146</v>
+        <v>-0.5587</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4051</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0179</v>
+        <v>-0.3357</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2381</v>
+        <v>-0.282</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2202</v>
+        <v>-0.0537</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3321</v>
+        <v>-0.1219</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9941</v>
+        <v>-0.3441</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9634</v>
+        <v>-0.039</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0307</v>
+        <v>-0.3051</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4253</v>
+        <v>-3.8974</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0757</v>
+        <v>-0.2553</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3496</v>
+        <v>-3.6421</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0563</v>
+        <v>-1.8586</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0563</v>
+        <v>-1.1845</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.369</v>
+        <v>-2.0388</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0194</v>
+        <v>0.9292</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3496</v>
+        <v>-2.968</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3735</v>
+        <v>-0.176</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0696</v>
+        <v>0.1171</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4431</v>
+        <v>-0.2931</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.534</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4545</v>
+        <v>-0.8323</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.247</v>
+        <v>-2.4547</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2074</v>
+        <v>1.6224</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.335</v>
+        <v>-2.7451</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0136</v>
+        <v>-2.34</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3486</v>
+        <v>-0.4051</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3249</v>
+        <v>-2.3255</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0233</v>
+        <v>-2.3255</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0101</v>
+        <v>-0.4196</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0097</v>
+        <v>-0.0146</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0004</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3501</v>
+        <v>0.0179</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1095</v>
+        <v>0.2381</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4596</v>
+        <v>-0.2202</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7693</v>
+        <v>0.3321</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0549</v>
+        <v>0.6093</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0427</v>
+        <v>-1.9941</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1664</v>
+        <v>-0.9634</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1237</v>
+        <v>-1.0307</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.731</v>
+        <v>-1.4253</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7644</v>
+        <v>-0.0757</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9666</v>
+        <v>-1.3496</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3066</v>
+        <v>-0.0563</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6102</v>
+        <v>-0.0563</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6964</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4245</v>
+        <v>-1.369</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1542</v>
+        <v>-0.0194</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2702</v>
+        <v>-1.3496</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0577</v>
+        <v>-0.3735</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0703</v>
+        <v>0.0696</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.128</v>
+        <v>-0.4431</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8789</v>
+        <v>-3.7614</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0771</v>
+        <v>-1.554</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8019</v>
+        <v>-2.2074</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9742</v>
+        <v>-0.642</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5032</v>
+        <v>0.7066</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.471</v>
+        <v>-1.3486</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2702</v>
+        <v>-0.6319</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9581</v>
+        <v>0.7163</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6879</v>
+        <v>-1.3482</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.704</v>
+        <v>-0.0101</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4549</v>
+        <v>-0.0097</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1589</v>
+        <v>-0.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
         <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3336</v>
+        <v>-0.3501</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1232</v>
+        <v>0.1095</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4568</v>
+        <v>-0.4596</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6177</v>
+        <v>-2.7693</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6177</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.9466</v>
+        <v>-4.0427</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.1195</v>
+        <v>-6.1664</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8271</v>
+        <v>2.1237</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.7337</v>
+        <v>-3.731</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7683</v>
+        <v>-0.7644</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.9654</v>
+        <v>-2.9666</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.9599</v>
+        <v>-3.3066</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.0185</v>
+        <v>-0.6102</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9414</v>
+        <v>-2.6964</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7739</v>
+        <v>-0.4245</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2502</v>
+        <v>-0.1542</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.0241</v>
+        <v>-0.2702</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3832</v>
+        <v>-0.0577</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2881</v>
+        <v>0.0703</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0951</v>
+        <v>-0.128</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4624</v>
+        <v>0.3321</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7396</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.514</v>
+        <v>-5.8789</v>
       </c>
       <c r="E26" t="n">
+        <v>-3.0771</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.8019</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.9742</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.5032</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.471</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2702</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.9581</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.704</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.1589</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.3336</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4568</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M. CASADO FAJO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-8.9466</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.1195</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.8271</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5.7337</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.7683</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-3.9654</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.9599</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.0185</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.9414</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.7739</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-2.0241</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.3832</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.2881</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.0951</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.4624</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.7396</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484232_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-22.5139</v>
+      </c>
+      <c r="E28" t="n">
         <v>-18.5191</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>-3.9948</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>-17.5121</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H28" t="n">
         <v>-2.672099999999999</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>-14.8401</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>-6.520799999999999</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>-3.152099999999999</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>-3.3686</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>-10.9917</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>0.4800000000000001</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>-11.4716</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>-2.9302</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-19.5342</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>-0.9079</v>
       </c>
-      <c r="T26" t="n">
-        <v>0.05620000000000003</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T28" t="n">
+        <v>0.05619999999999997</v>
+      </c>
+      <c r="U28" t="n">
         <v>-0.9641</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>-1.1638</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>7.4792</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-8.6432</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
